--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.44859259468393</v>
+        <v>2.510396296636139</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56136030516672</v>
+        <v>2.203721049589593</v>
       </c>
       <c r="E2" t="n">
-        <v>23.9675628433076</v>
+        <v>3.894728962037484</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4895278974903</v>
+        <v>1.867048283342173</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.0112927268124</v>
+        <v>4.714335068107015</v>
       </c>
       <c r="D3" t="n">
-        <v>27.77547387138886</v>
+        <v>4.51351450410069</v>
       </c>
       <c r="E3" t="n">
-        <v>23.9675628433076</v>
+        <v>3.894728962037484</v>
       </c>
       <c r="F3" t="n">
-        <v>11.4895278974903</v>
+        <v>1.867048283342173</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.69748942385354</v>
+        <v>11.6508420313762</v>
       </c>
       <c r="D4" t="n">
-        <v>41.70435924752847</v>
+        <v>6.776958377723376</v>
       </c>
       <c r="E4" t="n">
-        <v>23.9675628433076</v>
+        <v>3.894728962037484</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4895278974903</v>
+        <v>1.867048283342173</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
